--- a/data/trans_orig/P56S_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P56S_R-Estudios-trans_orig.xlsx
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4759</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>6097</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7952</t>
+          <t>8443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3244</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14486</t>
+          <t>15401</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18743</t>
+          <t>18646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1172</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>7,95%</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33472</t>
+          <t>32940</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1426,12 +1426,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,12 +1446,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52094</t>
+          <t>51497</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68878</t>
+          <t>68153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>87899</t>
+          <t>88153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107406</t>
+          <t>107806</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1496,12 +1496,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>69,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,52%</t>
         </is>
       </c>
     </row>
@@ -1524,12 +1524,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6796</t>
+          <t>7414</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>4065</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>16045</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1574,12 +1574,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,12 +1594,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5647</t>
+          <t>5914</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>19373</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1609,12 +1609,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4641</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,97%</t>
         </is>
       </c>
     </row>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>871</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2502,12 +2502,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4140</t>
+          <t>3819</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10037</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3275</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4881</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>58,3%</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>6468</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,53%</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5728</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,7 +4190,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>6209</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -4248,12 +4248,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4263,12 +4263,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,12 +4283,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>4509</t>
+          <t>4503</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>17374</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4298,12 +4298,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,12 +4318,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>6800</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>21181</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4333,12 +4333,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1144</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>10350</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>1151</t>
+          <t>1165</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>11353</t>
+          <t>10421</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -4474,12 +4474,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>35744</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>45004</t>
+          <t>44884</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>74,3%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,12 +4509,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>57529</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>75780</t>
+          <t>75649</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>97234</t>
+          <t>97613</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>117320</t>
+          <t>117862</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>68,56%</t>
+          <t>68,83%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -4587,12 +4587,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>929</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7709</t>
+          <t>7811</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4602,12 +4602,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>17262</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4637,12 +4637,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,12 +4657,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>7792</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>21243</t>
+          <t>21536</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4672,12 +4672,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,18%</t>
         </is>
       </c>
     </row>
@@ -5053,7 +5053,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4614</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>4965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -5166,7 +5166,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1099</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14190</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>26525</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>12565</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>29605</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -5427,7 +5427,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>8152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>7421</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,92%</t>
         </is>
       </c>
     </row>
@@ -5500,12 +5500,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1131</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5515,12 +5515,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5535,12 +5535,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9462</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25725</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5570,12 +5570,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>31459</t>
+          <t>31127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5585,12 +5585,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,24%</t>
         </is>
       </c>
     </row>
@@ -5613,12 +5613,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2223</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>12424</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5648,12 +5648,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>14992</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>32986</t>
+          <t>32762</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5663,12 +5663,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>19525</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40646</t>
+          <t>40848</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5698,12 +5698,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,06%</t>
         </is>
       </c>
     </row>
@@ -5726,12 +5726,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43469</t>
+          <t>43657</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58104</t>
+          <t>58207</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5761,12 +5761,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>95422</t>
+          <t>94686</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123169</t>
+          <t>122261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5776,12 +5776,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>143580</t>
+          <t>145686</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>176937</t>
+          <t>176344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5811,12 +5811,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,33%</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5859,77 +5859,77 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>13452</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>7357</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>22878</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>7,23%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>15508</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>9241</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>24110</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>6,1%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>3,63%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>9,48%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>13452</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>21120</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>3,91%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>15508</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>9019</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>24276</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -6556,12 +6556,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6591,12 +6591,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>966</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6788</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>35,41%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4442</t>
+          <t>4374</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10799</t>
+          <t>10775</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>19923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,37%</t>
         </is>
       </c>
     </row>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4246</t>
+          <t>4222</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4424</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,79%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -8116,7 +8116,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5748</t>
+          <t>5035</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>5160</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -8229,7 +8229,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6767</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>12038</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8279,7 +8279,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8294,12 +8294,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14656</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>7759</t>
+          <t>6955</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8357,7 +8357,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -8372,12 +8372,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>10015</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>25762</t>
+          <t>26855</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8387,12 +8387,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -8407,12 +8407,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11714</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>28766</t>
+          <t>29332</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8490,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>7214</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -8563,12 +8563,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1067</t>
+          <t>1068</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>10333</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8598,12 +8598,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13611</t>
+          <t>13149</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>30776</t>
+          <t>31599</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8613,12 +8613,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8633,12 +8633,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>17206</t>
+          <t>17292</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>37412</t>
+          <t>37697</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,43%</t>
         </is>
       </c>
     </row>
@@ -8676,12 +8676,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>13278</t>
+          <t>13249</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>33848</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8726,12 +8726,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>19903</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>41442</t>
+          <t>41222</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8761,12 +8761,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -8789,12 +8789,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>50636</t>
+          <t>51029</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>67396</t>
+          <t>67495</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8804,12 +8804,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>104310</t>
+          <t>104704</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>134279</t>
+          <t>133912</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8839,12 +8839,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>163431</t>
+          <t>164335</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>197192</t>
+          <t>197406</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8874,12 +8874,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,56%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,34%</t>
         </is>
       </c>
     </row>
@@ -8907,7 +8907,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>22064</t>
+          <t>21476</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8952,12 +8952,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>23752</t>
+          <t>24530</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9551,7 +9551,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>8649</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9566,7 +9566,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -9589,12 +9589,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1632</t>
+          <t>1607</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9056</t>
+          <t>9394</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9604,12 +9604,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9624,12 +9624,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2445</t>
+          <t>2501</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15173</t>
+          <t>14582</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9659,12 +9659,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>20479</t>
+          <t>18864</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9674,12 +9674,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
     </row>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11371</t>
+          <t>11063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10179</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>28019</t>
+          <t>28139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9885,12 +9885,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14995</t>
+          <t>15225</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>35162</t>
+          <t>36031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9900,12 +9900,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>18,07%</t>
         </is>
       </c>
     </row>
@@ -9928,12 +9928,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>756</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8784</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2359</t>
+          <t>2229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13202</t>
+          <t>13764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>4204</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>17273</t>
+          <t>17645</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -10041,12 +10041,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>35810</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>47952</t>
+          <t>47709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10056,12 +10056,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>63,44%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10076,12 +10076,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75013</t>
+          <t>74294</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100098</t>
+          <t>100107</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10091,12 +10091,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113430</t>
+          <t>113717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141894</t>
+          <t>142940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10126,12 +10126,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>71,68%</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6073</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10174,7 +10174,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13356</t>
+          <t>13576</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32619</t>
+          <t>32664</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10224,12 +10224,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>34358</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -10650,7 +10650,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6430</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6196</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10700,7 +10700,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -10836,12 +10836,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,09%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10871,12 +10871,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10886,12 +10886,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10906,12 +10906,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4046</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10921,12 +10921,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>42,82%</t>
         </is>
       </c>
     </row>
@@ -11062,12 +11062,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1788</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8048</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11097,12 +11097,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9141</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20331</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>36,01%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11132,12 +11132,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>26090</t>
+          <t>26380</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11147,12 +11147,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>72,15%</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11180,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6170</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11195,7 +11195,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11210,12 +11210,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11245,12 +11245,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2829</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13226</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11260,12 +11260,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>35,59%</t>
         </is>
       </c>
     </row>
@@ -11932,7 +11932,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -12158,7 +12158,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -12173,7 +12173,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,1%</t>
         </is>
       </c>
     </row>
@@ -12266,12 +12266,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12281,12 +12281,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,53%</t>
+          <t>90,56%</t>
         </is>
       </c>
     </row>
@@ -12579,7 +12579,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8552</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -12652,12 +12652,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1630</t>
+          <t>1602</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>9046</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12667,12 +12667,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -12687,12 +12687,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2892</t>
+          <t>2521</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>14888</t>
+          <t>16097</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12702,12 +12702,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -12722,12 +12722,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>6308</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>21278</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12737,12 +12737,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>5085</t>
+          <t>5130</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>16395</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12893,12 +12893,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -12913,12 +12913,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>15027</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>36644</t>
+          <t>37253</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12928,12 +12928,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12948,12 +12948,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>48625</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12963,12 +12963,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -12991,12 +12991,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -13026,12 +13026,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>13673</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -13046,7 +13046,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -13061,12 +13061,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>4601</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -13076,12 +13076,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -13104,12 +13104,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>41005</t>
+          <t>41406</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>56725</t>
+          <t>55912</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -13119,12 +13119,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -13139,12 +13139,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>86700</t>
+          <t>86382</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>116375</t>
+          <t>116254</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -13154,12 +13154,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>67,74%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>136363</t>
+          <t>135233</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>168629</t>
+          <t>167702</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13189,12 +13189,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,76%</t>
         </is>
       </c>
     </row>
@@ -13217,12 +13217,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>12832</t>
+          <t>12109</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13232,12 +13232,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -13252,12 +13252,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>18642</t>
+          <t>18906</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>41348</t>
+          <t>41034</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13267,12 +13267,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -13287,12 +13287,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>23786</t>
+          <t>23168</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>47572</t>
+          <t>47464</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -13302,12 +13302,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -13673,7 +13673,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -13683,22 +13683,22 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4822</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -13708,32 +13708,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>7311</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>3955</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11607</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -13743,32 +13743,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8641</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>15708</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -13786,32 +13786,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>2722</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9520</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -13821,32 +13821,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>14788</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>20987</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -13856,32 +13856,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>19051</t>
+          <t>20279</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13625</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25628</t>
+          <t>27824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,61%</t>
         </is>
       </c>
     </row>
@@ -13899,32 +13899,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17002</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -13934,32 +13934,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>44970</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34791</t>
+          <t>36719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51149</t>
+          <t>54164</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -13969,32 +13969,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>56573</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>44665</t>
+          <t>47568</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63827</t>
+          <t>67185</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -14012,7 +14012,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>1459</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -14022,12 +14022,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4948</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -14037,7 +14037,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -14047,27 +14047,27 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -14082,32 +14082,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2920</t>
+          <t>3089</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -14125,27 +14125,27 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2436</t>
+          <t>2605</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>682</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7075</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -14160,32 +14160,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14759</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21079</t>
+          <t>23752</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -14195,32 +14195,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>13266</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>24172</t>
+          <t>28081</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -14238,32 +14238,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1391</t>
+          <t>1540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>8785</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -14273,32 +14273,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5002</t>
+          <t>6167</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>15260</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -14308,32 +14308,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12346</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7968</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>20040</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -14351,32 +14351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39407</t>
+          <t>42039</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33060</t>
+          <t>34461</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>48193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>58,19%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>47,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -14386,32 +14386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>104973</t>
+          <t>113773</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>93916</t>
+          <t>102027</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>114795</t>
+          <t>124200</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>57,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -14421,32 +14421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>144380</t>
+          <t>155812</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>133461</t>
+          <t>143101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157111</t>
+          <t>169181</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,52%</t>
+          <t>58,46%</t>
         </is>
       </c>
     </row>
@@ -14464,32 +14464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2627</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -14499,32 +14499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8315</t>
+          <t>8721</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13006</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -14534,32 +14534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>11493</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7003</t>
+          <t>7419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -14577,17 +14577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>67905</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>67905</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>67905</t>
+          <t>72248</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -14612,17 +14612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>200561</t>
+          <t>217169</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>200561</t>
+          <t>217169</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>200561</t>
+          <t>217169</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -14647,17 +14647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>268466</t>
+          <t>289417</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>268466</t>
+          <t>289417</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>268466</t>
+          <t>289417</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -14729,32 +14729,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>558</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4712</t>
+          <t>4667</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -14764,32 +14764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1771</t>
+          <t>1813</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>549</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -14807,32 +14807,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5759</t>
+          <t>5842</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -14842,32 +14842,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2703</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>936</t>
+          <t>991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -14877,32 +14877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5456</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2575</t>
+          <t>2763</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9385</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -14920,32 +14920,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2718</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1016</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6152</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -14955,32 +14955,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4566</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2739</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8887</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -14990,32 +14990,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4270</t>
+          <t>4787</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>12985</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -15033,7 +15033,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>690</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -15043,12 +15043,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3384</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -15058,7 +15058,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -15068,32 +15068,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1733</t>
+          <t>1796</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>469</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4144</t>
+          <t>4335</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -15103,32 +15103,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5265</t>
+          <t>5427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -15146,7 +15146,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>497</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -15156,12 +15156,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -15181,67 +15181,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4836</t>
+          <t>5499</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>11,44%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5975</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>1,23%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>11,49%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>2181</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>4977</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -15259,32 +15259,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>1769</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>4575</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -15294,32 +15294,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2784</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8138</t>
+          <t>9894</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -15329,32 +15329,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3381</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10336</t>
+          <t>12226</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,95%</t>
         </is>
       </c>
     </row>
@@ -15372,32 +15372,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>18247</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12819</t>
+          <t>13599</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>21863</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,46%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -15407,17 +15407,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>21711</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28343</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -15427,12 +15427,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -15442,32 +15442,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>45140</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34419</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>51657</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>67,39%</t>
         </is>
       </c>
     </row>
@@ -15485,32 +15485,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>496</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -15520,32 +15520,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1618</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>380</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4210</t>
+          <t>4366</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -15555,32 +15555,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3423</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1340</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>7711</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -15598,17 +15598,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27102</t>
+          <t>28593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -15633,17 +15633,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42074</t>
+          <t>48062</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -15668,17 +15668,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>76655</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>76655</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69176</t>
+          <t>76655</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -15863,7 +15863,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>485</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -15873,12 +15873,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2582</t>
+          <t>2553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -15888,7 +15888,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -15898,7 +15898,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>490</t>
+          <t>485</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -15908,12 +15908,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2584</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -15976,7 +15976,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -15986,12 +15986,12 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>3349</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -16001,7 +16001,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -16021,12 +16021,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>24,62%</t>
         </is>
       </c>
     </row>
@@ -16167,7 +16167,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>617</t>
+          <t>601</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -16177,12 +16177,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -16192,7 +16192,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -16202,7 +16202,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>405</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -16212,12 +16212,12 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1707</t>
+          <t>2424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -16237,7 +16237,7 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1000</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
@@ -16247,12 +16247,12 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -16262,7 +16262,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -16393,32 +16393,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2405</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>5974</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -16428,32 +16428,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1312</t>
+          <t>1846</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>74,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -16463,32 +16463,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>9346</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>5052</t>
+          <t>6312</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10065</t>
+          <t>11965</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>41,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>78,13%</t>
         </is>
       </c>
     </row>
@@ -16506,7 +16506,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -16516,12 +16516,12 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3298</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -16541,32 +16541,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>2358</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3949</t>
+          <t>4773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -16576,32 +16576,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>3412</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1086</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -16619,17 +16619,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6476</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -16654,17 +16654,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>6469</t>
+          <t>8168</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -16689,17 +16689,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>12945</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -16736,32 +16736,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2152</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5219</t>
+          <t>6297</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -16771,32 +16771,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9124</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -16806,27 +16806,27 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>11276</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6528</t>
+          <t>6553</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>15912</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -16849,32 +16849,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>7896</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -16884,32 +16884,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>16970</t>
+          <t>18129</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>12295</t>
+          <t>13020</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>25567</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -16919,32 +16919,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>24865</t>
+          <t>26220</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>32688</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -16962,32 +16962,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>13960</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>9407</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20516</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -16997,32 +16997,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>47286</t>
+          <t>51457</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>38443</t>
+          <t>43433</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>55698</t>
+          <t>63023</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -17032,32 +17032,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>61245</t>
+          <t>65729</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>54737</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>72453</t>
+          <t>76844</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -17075,32 +17075,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2149</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>556</t>
+          <t>558</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6261</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -17110,32 +17110,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>3286</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>1609</t>
+          <t>1551</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>6150</t>
+          <t>6916</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -17145,32 +17145,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>3121</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -17188,32 +17188,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>3518</t>
+          <t>3703</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7843</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -17223,32 +17223,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>16858</t>
+          <t>19146</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>13547</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23250</t>
+          <t>27170</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -17258,32 +17258,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>20376</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -17301,32 +17301,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2601</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10152</t>
+          <t>11028</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -17336,22 +17336,22 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>13090</t>
+          <t>14899</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>9037</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>18990</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -17361,7 +17361,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -17371,32 +17371,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>18572</t>
+          <t>20796</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>13179</t>
+          <t>15262</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>25329</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -17414,32 +17414,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>61290</t>
+          <t>65778</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>52395</t>
+          <t>57478</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>68592</t>
+          <t>73859</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>51,63%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -17449,32 +17449,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>131446</t>
+          <t>144520</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>119963</t>
+          <t>132163</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>142117</t>
+          <t>155897</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -17484,32 +17484,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>192736</t>
+          <t>210298</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>179004</t>
+          <t>194261</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>205659</t>
+          <t>225628</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>58,66%</t>
+          <t>59,16%</t>
         </is>
       </c>
     </row>
@@ -17527,32 +17527,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2986</t>
+          <t>2998</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>9894</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -17562,32 +17562,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>12697</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>7206</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>16599</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -17597,17 +17597,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>17135</t>
+          <t>18644</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>12066</t>
+          <t>13228</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>23214</t>
+          <t>25730</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -17617,12 +17617,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -17640,17 +17640,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>101483</t>
+          <t>107989</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>101483</t>
+          <t>107989</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>101483</t>
+          <t>107989</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -17675,17 +17675,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>249104</t>
+          <t>273399</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>249104</t>
+          <t>273399</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>249104</t>
+          <t>273399</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -17710,17 +17710,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>350587</t>
+          <t>381388</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>350587</t>
+          <t>381388</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>350587</t>
+          <t>381388</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
